--- a/www/download/COUNTRY.CAN.EXI382.xlsx
+++ b/www/download/COUNTRY.CAN.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Canadá</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -967,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2848</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2848</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2848</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2848</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2848</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2848</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2848</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2848</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2848</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2848</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2848</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2848</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2848</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2848</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2848</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2848</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2848</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2848</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2848</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2848</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2848</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2848</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2848</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2848</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2848</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2848</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.2848</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>14.022</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>13.292</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>12.019</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>12.699</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>12.976</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>14.741</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>15.086</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>15.176</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>15.609</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>15.942</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>16.208</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>14.902</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>16.725</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>17.099</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>17.378</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>15.837</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>17.385</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>17.683</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>17.851</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>16.651</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>15.496</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>15.501</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>14.858</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>14.897</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>14.306</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14.983</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>14.557</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>12.472</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>11.717</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>10.609</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>11.227</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>11.452</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>13.03</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>13.466</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>13.649</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>14.043</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>14.353</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>14.64</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>13.48</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>15.155</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>15.468</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>15.765</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>14.251</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>15.751</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>16.06</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>16.248</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>15.129</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>14.055</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>13.974</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>13.404</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13.378</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>12.807</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13.417</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>12.994</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>24884.716</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>23719.492</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>21711.029</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>22951.165</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>23392.199</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>26231.013</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>26804.392</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>26856.964</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>27348.689</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>27718.698</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>28497.801</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>26299.86</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>29149.991</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>29741.591</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>30108.649</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>27203.083</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>29580.123</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>30027.806</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>30541.025</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>28431.563</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>26426.583</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>26317.661</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>25215.392</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>25195.53</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>24350.853</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>25614.49</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>25074.842</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>22214.536</t>
+          <t>79133303147.2553</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>17985.769</t>
+          <t>24177892598.5451</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>16229.934</t>
+          <t>23134559694.6877</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>17245.597</t>
+          <t>23726306573.7353</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>17459.259</t>
+          <t>24869515432.8446</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>20014.963</t>
+          <t>28290652436.9984</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20872.578</t>
+          <t>28424599089.1251</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>21236.468</t>
+          <t>28805605551.3364</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>21809.679</t>
+          <t>28546801188.786</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>22109.072</t>
+          <t>32834299969.0709</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>22836.023</t>
+          <t>33697267043.2802</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>21030.285</t>
+          <t>31148158607.9911</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>23636.213</t>
+          <t>31998348303.5313</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>24020.325</t>
+          <t>33294130381.4271</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>24550.087</t>
+          <t>32736048708.4801</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>21759.22</t>
+          <t>30944861164.3035</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>24161.939</t>
+          <t>34918658541.3879</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>24734.01</t>
+          <t>37046087501.248</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>25282.339</t>
+          <t>37559106168.093</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>25911.377</t>
+          <t>31169297235.9239</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>24044.565</t>
+          <t>29474758362.0053</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>23792.119</t>
+          <t>30026229483.8592</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>22809.74</t>
+          <t>27788318985.9935</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>22699.796</t>
+          <t>29471612813.1753</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>21895.216</t>
+          <t>27950462792.9373</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>23063.805</t>
+          <t>29177411715.5577</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>22526.507</t>
+          <t>31160468932.0707</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>107521170128.009</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>12565812061.7297</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>10255989872.1644</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>11184810776.278</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>12410080291.4961</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>13145056407.8043</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>13993100927.2131</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>14302493002.4927</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>14470158431.3952</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>14879944587.4623</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>15339793635.4607</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>14583034679.6431</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>14784901147.843</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>15594982083.2656</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>15592997203.4528</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>15238827792.9433</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>17030750806.9187</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>18363891424.1735</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>17415077723.7868</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>16485681867.6548</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>16027084585.3584</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>17522921414.4571</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>17314434813.2546</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17586158005.7895</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>17481942081.6151</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>19006117581.4826</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>17764861997.558</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>17518811.5353042</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>5099220.74615977</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>5426400.9795316</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>4722175.70295634</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>4331141.68470213</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>4478863.02636054</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3493790.63348464</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>4279002.20583518</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>3923876.45196119</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>4122753.28069388</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>3918815.69790213</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>3898636.51942733</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>3024624.02055366</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>3244786.62820269</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>3638515.82494136</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>3019469.43141418</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>3037001.76882673</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>3036127.06041043</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2772933.43305749</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>3707408.01642715</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>4073261.08475371</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>3202942.0213392</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>3144154.59155431</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>3242640.60112117</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2912248.64499961</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>3060480.52014032</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2958379.39043086</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>44750.3577180234</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>92044.3271351967</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>82082.8227900045</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>90341.7582685322</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>95636.27218748</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>140448.97667167</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>143413.600698631</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>138406.435441311</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>128749.421662347</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>126431.682981776</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>139627.278010606</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>124058.103248512</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>158072.835630678</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>160736.712624488</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>160853.152630842</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>154417.370033312</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>190304.837699021</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>213882.426160889</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>213281.833222183</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>208059.683993352</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>213970.153921293</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>189844.270148103</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>190978.871911273</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>192093.784185029</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>199681.918116031</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>192514.135014267</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>189199.590986082</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>294977.509845218</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>183729.557052098</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>191476.052434578</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>201885.743279252</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>223211.233699295</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>303525.132927072</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>306211.141963916</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>300806.473974457</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>273843.227791191</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>307802.57703969</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>338649.843279917</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>334852.357893839</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>356394.79232769</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>372611.577412724</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>367139.667280775</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>400221.021417722</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>470155.670247203</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>550554.839724654</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>545244.764846862</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>468357.30467842</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>500308.8853203</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>464548.940940255</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>454536.052635406</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>468847.81725943</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>473756.731361838</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>470469.921141671</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>493290.794126508</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-0.793393843842962</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.431325640686062</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.582483426981921</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0.541876509576505</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.406861083080154</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.52262283090088</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.491633492002229</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.48480883691388</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.507217706246726</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.485830264356236</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.488678631713657</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.442106218766317</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.598672372824419</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.540259865112379</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.574430283009295</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.427880168714479</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.418724240282774</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.346882827211984</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.451749995090324</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0.571750421786533</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>0.500245709318491</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>0.357771272440317</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>0.317382897159499</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>0.29077628914767</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>0.252447561685155</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>0.213493754536109</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>0.268037235716906</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>8620.95816924632</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1072.45101837709</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>966.750924914754</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>996.285646766278</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1083.67045729087</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1008.79721174138</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1039.10914296679</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1047.84697671876</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1030.38964120069</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1036.71753574296</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1047.76468524189</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1081.81385543671</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>975.601623781654</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1008.20673357853</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>989.088637305592</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1069.29987698924</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1081.28009582657</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1143.48907730281</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1071.85275669486</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1089.70992271385</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>1140.32182498318</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>1254.00314997662</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>1291.76602710482</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>1314.57209955191</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1365.00356226684</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>1416.60565269788</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1367.18327135857</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>125761318122.485</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>12889671714.8898</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>11545624417.2707</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>11973009304.0352</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>15697018274.564</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>18980764227.2406</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>19937964048.7137</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.453</t>
+          <t>18640810704.8368</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>18204769501.5276</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>23029875350.5542</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>23877487917.2727</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>22270553028.9846</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>17774357563.1213</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>19799845730.609</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>11743128987.317</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.648</t>
+          <t>13096986332.5307</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.706</t>
+          <t>15224227200.7354</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.752</t>
+          <t>15046486894.9661</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.746</t>
+          <t>15058127677.5647</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.712</t>
+          <t>13736962782.4808</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.762</t>
+          <t>10625979040.8097</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.742</t>
+          <t>13257178460.9185</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.791</t>
+          <t>13868113200.1442</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.792</t>
+          <t>14330522560.1862</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>14551862779.6871</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.882</t>
+          <t>16852697794.3858</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>17154558189.4272</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>128688841229.939</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>13947549056.623</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>13128134791.9283</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>13168296497.9297</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>16640531943.3397</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>20443007235.9154</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>21290723122.6204</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>20213140578.2681</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>19498457230.2999</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>23972558913.7727</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>25416460086.4167</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>24891410702.8219</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>19398122456.9866</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>21829664266.102</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>15085795230.4502</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>17100628621.984</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>17711032231.3554</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>17774618891.2771</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>17833698394.7927</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>16103033982.131</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>13261718650.903</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>16913608387.8271</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>16748265536.4759</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17169781251.1813</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>16997785185.9685</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>19521892445.5796</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>18728311130.8018</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-2927523107.45405</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-1057877341.73316</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-1582510374.6576</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-1195287193.89451</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-943513668.775637</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-1462243008.67485</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-1352759073.90676</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-1572329873.43132</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-1293687728.7723</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-942683563.218528</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>-1538972169.14401</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>-2620857673.83731</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>-1623764893.86534</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>-2029818535.49298</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>-3342666243.13325</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>-4003642289.4533</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>-2486805030.61994</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>-2728131996.31098</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>-2775570717.22803</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>-2366071199.6502</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-2635739610.09338</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>-3656429926.90868</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>-2880152336.33165</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>-2839258690.99507</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>-2445922406.2814</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>-2669194651.19377</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-1573752941.37461</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.852</t>
+          <t>1781.1430297386</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.931</t>
+          <t>1535.02664098301</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.081</t>
+          <t>1529.86731669704</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.057</t>
+          <t>1536.14943557716</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1.202</t>
+          <t>1524.5737932462</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.539</t>
+          <t>1536.01766634658</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.572</t>
+          <t>1549.969999495</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1555.85245076551</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.494</t>
+          <t>1553.02151155089</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.566</t>
+          <t>1540.38629019571</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.785</t>
+          <t>1559.78489798379</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.986</t>
+          <t>1560.09048847285</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2.011</t>
+          <t>1559.66736282237</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.977</t>
+          <t>1552.90036746707</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>1557.25110315432</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2.314</t>
+          <t>1526.83208876177</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>2.392</t>
+          <t>1534.03828248444</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2.709</t>
+          <t>1540.14580132363</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>2.587</t>
+          <t>1556.06223426931</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2.567</t>
+          <t>1712.75203065046</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>2.583</t>
+          <t>1710.76292517324</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2.596</t>
+          <t>1702.64945258792</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>1701.75047123957</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>2.694</t>
+          <t>1696.81849647668</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>1709.59538325266</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>1719.04211218942</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>2.972</t>
+          <t>1733.63929613191</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>1774.6466887192</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>1784.49517340899</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>1806.46293681434</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>1807.25305573661</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>1802.67316153732</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>1779.46979546411</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>1776.8285823661</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.453</t>
+          <t>1769.68696194237</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>1752.11923694862</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>1738.71930909639</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1758.2275821801</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1764.84846044648</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>1742.86283994035</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>1739.38113158957</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>1732.62158962906</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.648</t>
+          <t>1717.70794065772</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.706</t>
+          <t>1701.48902679281</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.752</t>
+          <t>1698.1627906649</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.746</t>
+          <t>1710.90607194431</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.712</t>
+          <t>1707.47867873222</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.762</t>
+          <t>1705.41927811258</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.742</t>
+          <t>1697.79623248611</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.791</t>
+          <t>1697.03989855896</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.792</t>
+          <t>1691.34071259268</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1702.10236411821</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.882</t>
+          <t>1709.61810753516</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>1722.47323212501</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>193003.049194211</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>177509.505580664</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>221478.757033123</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>228948.881797815</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>277508.900299614</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>353863.8425469</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>343894.486017847</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>339323.381232045</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>313333.842762334</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>334167.715717404</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>383563.556003816</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>414108.990900165</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>396460.92943729</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>389147.190601459</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>294738.697003217</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>370008.465508066</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>419874.793287105</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>481382.264168861</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>468266.187347349</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>482047.620017691</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>508454.155962447</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>508491.223032606</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>537775.262334567</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>550452.460407917</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>582912.451006623</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>602278.263480871</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>613877.772868915</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>25103031820.6676</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>5013923048.24491</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>5940471325.59612</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>6382172483.2012</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>7155174913.66232</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>7515988603.6815</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>7295380353.49819</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>7502567559.83152</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>6917550894.25221</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>8308254659.63313</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>8531855573.03083</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>8343779221.88923</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>7175974091.56886</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>7028256877.10225</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>6475268820.06582</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>6080025112.11541</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>6640793190.93615</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>7568009962.67128</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>7749873536.86793</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>6531933057.51987</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>7086391569.57757</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>7425596145.39308</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>7825064211.11947</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>8685189765.03304</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>8122470481.57775</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>8750754647.34574</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>8850232901.41916</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>174010.563829635</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>151946.840459098</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>206884.655485295</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>214314.96180013</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>247433.222558641</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>294183.256611971</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>281995.81729305</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>292892.187601963</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>273003.496945315</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>285975.663235725</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>334775.39979966</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>376281.53137739</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>365980.230913083</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>364757.23712521</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>313326.463199865</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>399876.512197543</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>439101.500644764</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>516539.407236522</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>496775.81394591</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>498122.291054625</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>553655.45406133</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>551111.68346743</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>579628.208481087</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>586527.214256419</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>615382.781617506</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>626919.964897271</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>643399.144394673</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>24884.716</t>
+          <t>140104608627.033</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>23719.492</t>
+          <t>12710844847.7797</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>21711.029</t>
+          <t>14754259189.739</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>22951.165</t>
+          <t>15598175836.9532</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>23392.199</t>
+          <t>17334993783.1316</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>26231.013</t>
+          <t>17237872210.8617</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>26804.392</t>
+          <t>17250389717.1812</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>26856.964</t>
+          <t>18373881769.0762</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>27348.689</t>
+          <t>18271095738.6141</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>27718.698</t>
+          <t>22500197136.7992</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>28497.801</t>
+          <t>24249495857.4232</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>26299.86</t>
+          <t>24985920257.1532</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>29149.991</t>
+          <t>21165165235.8047</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>29741.591</t>
+          <t>23485719250.2797</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>30108.649</t>
+          <t>20954357322.3269</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>27203.083</t>
+          <t>22859801826.9324</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>29580.123</t>
+          <t>24082162672.6863</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>30027.806</t>
+          <t>26447723463.9066</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>30541.025</t>
+          <t>26073880344.5677</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>28431.563</t>
+          <t>21977731306.8281</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>26426.583</t>
+          <t>22081748820.7446</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26317.661</t>
+          <t>25202952821.2342</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>25215.392</t>
+          <t>25724568573.6343</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>25195.53</t>
+          <t>26601171509.8322</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>24350.853</t>
+          <t>25637816111.2509</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>25614.49</t>
+          <t>27994715832.6011</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>25074.842</t>
+          <t>28881208109.6245</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>22214.536</t>
+          <t>18992.4853645754</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>17985.769</t>
+          <t>25562.6651215666</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>16229.934</t>
+          <t>14594.1015478284</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>17245.597</t>
+          <t>14633.9199976854</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>17459.259</t>
+          <t>30075.6777409726</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>20014.963</t>
+          <t>59680.5859349289</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>20872.578</t>
+          <t>61898.668724797</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>21236.468</t>
+          <t>46431.1936300813</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>21809.679</t>
+          <t>40330.345817019</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>22109.072</t>
+          <t>48192.0524816785</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>22836.023</t>
+          <t>48788.1562041555</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>21030.285</t>
+          <t>37827.4595227745</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>23636.213</t>
+          <t>30480.6985242069</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>24020.325</t>
+          <t>24389.9534762493</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>24550.087</t>
+          <t>-18587.7661966474</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>21759.22</t>
+          <t>-29868.0466894763</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>24161.939</t>
+          <t>-19226.707357659</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>24734.01</t>
+          <t>-35157.1430676611</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>25282.339</t>
+          <t>-28509.6265985611</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>25911.377</t>
+          <t>-16074.6710369343</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>24044.565</t>
+          <t>-45201.2980988829</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>23792.119</t>
+          <t>-42620.4604348239</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>22809.74</t>
+          <t>-41852.9461465199</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>22699.796</t>
+          <t>-36074.7538485016</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>21895.216</t>
+          <t>-32470.3306108835</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>23063.805</t>
+          <t>-24641.7014163997</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>22526.507</t>
+          <t>-29521.3715257585</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>74701.782</t>
+          <t>-115001576806.365</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>22651.077</t>
+          <t>-7696921799.53477</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>21571.632</t>
+          <t>-8813787864.1429</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>22120.454</t>
+          <t>-9216003353.75205</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>22977.015</t>
+          <t>-10179818869.4693</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>26193.381</t>
+          <t>-9721883607.18017</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>26283.342</t>
+          <t>-9955009363.68302</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>26586.712</t>
+          <t>-10871314209.2447</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>26545.755</t>
+          <t>-11353544844.3618</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>30081.083</t>
+          <t>-14191942477.166</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>30958.75</t>
+          <t>-15717640284.3924</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>28431.425</t>
+          <t>-16642141035.264</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>29752.068</t>
+          <t>-13989191144.2358</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>30688.211</t>
+          <t>-16457462373.1774</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>30027.947</t>
+          <t>-14479088502.2611</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>28131.652</t>
+          <t>-16779776714.817</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>31641.285</t>
+          <t>-17441369481.7501</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>33536.202</t>
+          <t>-18879713501.2353</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>33974.998</t>
+          <t>-18324006807.6998</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>28615.564</t>
+          <t>-15445798249.3082</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>26908.617</t>
+          <t>-14995357251.1671</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>27358.628</t>
+          <t>-17777356675.8411</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>25712.626</t>
+          <t>-17899504362.5148</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>27133.752</t>
+          <t>-17915981744.7992</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>25823.667</t>
+          <t>-17515345629.6731</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>26843.391</t>
+          <t>-19243961185.2553</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>28465.293</t>
+          <t>-20030975208.2054</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>169240.988993661</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>161936.493379223</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>187088.186140171</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>185171.40301379</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>235423.019089892</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.244</t>
+          <t>287305.767656898</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>297884.542955091</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>292248.890190999</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>284297.195298594</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>288198.017130262</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>283928.777303379</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.267</t>
+          <t>319308.967530125</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>344302.899798555</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>315263.068288247</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.294</t>
+          <t>310641.77598357</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>401692.196689434</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>445802.293838396</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>474507.910589389</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.428</t>
+          <t>478529.053724614</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>452965.498720316</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.389</t>
+          <t>449261.270715353</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.359</t>
+          <t>460556.02228969</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>512090.16960936</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>507246.438025099</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>539597.001758074</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>555803.114797447</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.377</t>
+          <t>555742.770313006</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>12005.131</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>12112.574</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>9917.428</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>10617.274</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>10655.502</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>13090.821</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>13312.625</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>13253.974</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>13421.49</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>13486.878</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>13893.577</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>11539.956</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>14192.322</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>14362.38</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>14342.489</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>11939.463</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>14134.02</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>14391.858</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>14691.888</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>13846.425</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>12605.65</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>12270.629</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>11675.601</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>12074.949</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>11780.734</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11939.263</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>11951.466</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>356612.496345456</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>365579.587323201</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>389271.929843819</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>387549.155432561</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>462124.656787504</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>572435.08872821</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>596140.759163547</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>581849.425756318</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>572829.926567168</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>567928.467966216</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>616395.785165716</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>693354.838594691</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>720034.356954033</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>693985.688594176</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>672558.542730378</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>832724.640226658</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>906628.219428936</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>966796.843627544</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>959070.721360659</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>914547.585718988</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>978666.993958838</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>953210.461761621</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>1015705.44055156</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>1017305.29355856</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>1118405.63541209</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>1133019.34872544</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>1042524.94669946</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>109278.33</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>11634.867</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>9458.421</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>10307.113</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>11343.188</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>12146.273</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>12867.996</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>13234.271</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>13588.637</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>13869.618</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>14413.766</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>13550.335</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>14019.862</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>14593.626</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>14523.908</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>13947.522</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>15674.634</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>16818.91</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>16049.824</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>15231.24</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>14793.005</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>16108.021</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>16229.398</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>16404.771</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>16341.1</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>17738.996</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>16419.304</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>-79.67</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>54.59</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>71.59</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>67.32</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>53.92</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>64.78</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>62.21</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>60.47</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>60.5</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>59.41</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>58.43</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>55.2</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>68.59</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>64.59</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>69.03</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>56.01</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>54.15</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>47.06</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>57.52</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>70.12</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>62.54</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>47.7</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>40.55</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>38.37</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>33.99</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>30.02</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>37.2</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>21.446</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>6.194</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>6.669</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>5.715</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>5.202</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>5.337</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>4.116</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>4.982</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>4.644</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>4.851</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>4.629</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>4.648</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>3.598</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>3.787</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>4.202</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>3.414</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>3.389</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>3.37</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>3.157</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>4.366</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>4.98</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>3.79</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>3.835</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>3.929</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>3.534</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>3.717</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>3.55</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>223426.737707553</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>253899.16671839</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>295920.222438696</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>283779.650002947</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>283354.439012618</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>373110.302495714</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>371509.43416901</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>363064.438413615</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>360936.46679015</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>421512.414097751</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>511832.75476202</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>564519.411043006</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>563787.072462038</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>572259.660248172</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>508147.06795175</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>634975.451189033</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>614620.408729353</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>743163.746252589</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>680934.096699912</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>715312.684170483</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>668268.121905297</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>701257.628779948</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>698077.451565583</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>694956.762882749</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>656523.616565782</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>731560.217508362</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>877153.285981553</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>22214535665.655</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>17985768999.9959</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>16229933999.9947</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>17245597000.0012</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>17459259000.0059</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>20014963000.0028</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>20872577999.9986</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>21236468000.0001</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>21809678999.9942</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>22109071999.9953</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>22836023000.0074</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>21030284999.9982</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>23636212999.9967</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>24020325000.0006</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>24550086999.9954</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>21759219999.9987</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>24161938999.9911</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>24734010000.0047</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>25282339000.0052</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>25911377428.925</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>24044564882.0684</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>23792119305.7791</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>22809740296.9647</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>22699795771.0775</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>21895215733.6399</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>23063804983.1081</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>22526506500.2757</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>24884715891.5985</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>23719491999.996</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>21711028999.9954</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>22951165000.0009</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>23392199000.0057</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>26231013000.0021</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>26804391999.9978</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>26856964000.0007</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>27348688999.9959</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>27718697999.9945</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>28497801000.0082</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>26299859999.9983</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>29149990999.9969</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>29741590999.9995</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>30108648999.9963</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>27203082999.9994</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>29580122999.9906</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>30027806000.0042</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>30541025000.005</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>28431563102.2932</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>26426583135.0825</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>26317660721.2692</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>25215391848.2891</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>25195529723.3985</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>24350853309.1604</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>25614489719.3908</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>25074842275.9537</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>12005130916.9524</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>12112573999.9966</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>9917427999.99831</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>10617274000</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>10655502000.0043</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>13090821000.0027</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>13312624999.9969</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>13253973999.9993</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>13421489999.9963</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>13486877999.9942</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>13893577000.0067</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>11539956000</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>14192321999.9988</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>14362380000.002</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>14342488999.9936</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>11939462999.9966</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>14134019999.9978</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>14391858000.01</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>14691888000.0019</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>13846424660.023</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>12605649766.6908</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>12270628817.117</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>11675601487.4633</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>12074949318.1201</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>11780733978.557</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11939263119.6167</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>11951465640.7116</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>14022349.3779251</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>13291989.9999975</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>12018530.0000023</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>12699475.0000001</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>12976394.9999993</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>14740914.999999</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>15085524.9999997</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>15176109.9999986</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>15608920.0000022</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>15942019.9999963</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>16208254.9999998</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>14902050.000001</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>16725350.0000003</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>17098950.0000034</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>17377510.0000008</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>15836849.9999966</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>17384844.9999981</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>17682525.0000013</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>17850790.0000013</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>16651196.5604181</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>15495651.6994046</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>15501071.4582232</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>14858455.5199325</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14896779.5405197</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>14306338.9267869</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14982579.7974967</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>14557464.1209483</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>12472067.2594807</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>11716909.9999972</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>10608720.0000029</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>11226509.9999999</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>11451894.9999991</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>13030424.9999991</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>13466439.9999994</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>13649409.999998</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>14043385.000002</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>14352939.9999959</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>14640495.0000001</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>13480170.0000008</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>15154650.0000004</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>15468040.0000034</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>15765015.0000006</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>14251219.9999969</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>15750544.9999981</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>16059525.0000018</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>16247640.0000012</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>15128504.8654034</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>14054878.3985563</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>13973586.4417755</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>13403692.6579194</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13377857.3360745</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>12807250.1529469</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13416660.8366175</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>12993767.8215628</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>24884715891.5985</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>23719491999.996</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>21711028999.9954</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>22951165000.0009</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>23392199000.0057</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>26231013000.0021</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>26804391999.9978</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>26856964000.0007</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>27348688999.9959</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>27718697999.9945</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>28497801000.0082</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>26299859999.9983</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>29149990999.9969</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>29741590999.9995</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>30108648999.9963</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>27203082999.9994</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>29580122999.9906</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>30027806000.0042</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>30541025000.005</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>28431563102.2932</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>26426583135.0825</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>26317660721.2692</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>25215391848.2891</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>25195529723.3985</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>24350853309.1604</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>25614489719.3908</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>25074842275.9537</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>22214535665.655</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>17985768999.9959</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>16229933999.9947</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>17245597000.0012</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>17459259000.0059</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>20014963000.0028</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>20872577999.9986</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>21236468000.0001</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>21809678999.9942</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>22109071999.9953</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>22836023000.0074</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>21030284999.9982</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>23636212999.9967</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>24020325000.0006</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>24550086999.9954</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>21759219999.9987</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>24161938999.9911</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>24734010000.0047</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>25282339000.0052</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>25911377428.925</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>24044564882.0684</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>23792119305.7791</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>22809740296.9647</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>22699795771.0775</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>21895215733.6399</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>23063804983.1081</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>22526506500.2757</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1094567.24887789</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1196368.71342961</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1388512.44522066</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1358549.17437294</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1544316.3884376</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1977133.45667512</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2020023.9471052</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1962304.62301686</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1919057.82475978</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2012116.2178132</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2293867.98404423</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2551381.91895805</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2583098.12262069</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2539633.58614257</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2355505.25582458</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>2972666.02833856</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>3072615.11391828</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>3479961.97793935</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>3324410.63826326</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>3298268.8885471</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>3319076.04235897</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>3334835.82741264</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>3469583.23267045</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>3460899.95867919</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>3687904.38503729</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>3699641.36968888</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>3818266.88721208</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>371768.709658813</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>384223.199151082</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>446183.775044952</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>442820.354917973</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>534448.206600535</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>662928.418342188</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>688645.159251259</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>670434.481200263</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>656244.315456864</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>638925.802771378</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>699704.548443422</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>785496.672151324</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>813187.112296147</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>784286.139216793</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>758068.534774726</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>932395.975602146</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1040143.58283661</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1085521.57984688</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>1106048.06881074</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1028895.54282362</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>1133727.55949607</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>1072605.24958314</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>1177909.06645054</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>1178289.97346366</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>1342114.23532408</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>1302273.64695299</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>1192394.70114042</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3614,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3637,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3678,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4039,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
